--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260512_210938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260512_210938.xlsx
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260512_210938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260512_210938.xlsx
@@ -6224,7 +6224,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
